--- a/Option-Scanner/Production/Ledger.xlsx
+++ b/Option-Scanner/Production/Ledger.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1073,6 +1073,285 @@
         <v>0</v>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-06-03 09:57:24</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>TEST-BUY-ea4f07cba299</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NIFTY 09 JUN 23350 PUT</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>BUY_TIMEOUT/FAILED</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>247.1</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-06-03 09:58:24</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>TEST-BUY-346853f2de02</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NIFTY 09 JUN 23350 PUT</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>BUY_TIMEOUT/FAILED</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>247.1</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-06-03 09:59:25</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>TEST-BUY-5b753764b245</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NIFTY 09 JUN 23350 PUT</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>BUY_TIMEOUT/FAILED</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>247.1</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-06-03 10:32:52</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>TEST-BUY-33ef29913b97</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>BUY_TIMEOUT/FAILED</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>23241.7</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-06-03 10:33:53</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>TEST-BUY-938d5c620537</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>BUY_TIMEOUT/FAILED</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="n">
+        <v>23241.7</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-06-03 10:34:55</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>TEST-BUY-87fa4a067ba8</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>BUY_TIMEOUT/FAILED</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>23241.7</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-06-03 11:11:34</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>TEST-BUY-35a9e19ce276</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NIFTY 09 JUN 23300 PUT</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>BUY_TIMEOUT/FAILED</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>231.9</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-06-03 11:12:34</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>TEST-BUY-29abf7cf17e7</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NIFTY 09 JUN 23300 PUT</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>BUY_TIMEOUT/FAILED</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
+        <v>231.9</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-06-03 11:13:34</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>TEST-BUY-82948dee463f</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NIFTY 09 JUN 23300 PUT</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>BUY_TIMEOUT/FAILED</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="n">
+        <v>231.9</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Option-Scanner/Production/Ledger.xlsx
+++ b/Option-Scanner/Production/Ledger.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1352,6 +1352,471 @@
         <v>0</v>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-06-04 13:16:37</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>TEST-BUY-1e30473fd20f</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NIFTY 09 JUN 23300 PUT SEDA</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>BUY_TIMEOUT/FAILED</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="n">
+        <v>148.5</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-06-04 13:17:40</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>TEST-BUY-34f4c9eea434</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NIFTY 09 JUN 23300 PUT SEDA</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>BUY_TIMEOUT/FAILED</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="n">
+        <v>148.5</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-06-04 13:18:40</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>TEST-BUY-fd2fc060e0ea</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NIFTY 09 JUN 23300 PUT SEDA</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>BUY_TIMEOUT/FAILED</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" t="n">
+        <v>148.5</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-06-04 13:20:07</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>TEST-BUY-09d5f140077a</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>NIFTY 09 JUN 23350 PUT SEDA</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>BUY_TIMEOUT/FAILED</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="n">
+        <v>162.3</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-06-04 13:21:07</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>TEST-BUY-d0f4b24ba633</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>NIFTY 09 JUN 23350 PUT SEDA</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>BUY_TIMEOUT/FAILED</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="n">
+        <v>162.3</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-06-04 13:22:07</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>TEST-BUY-4568b4107cfe</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>NIFTY 09 JUN 23350 PUT SEDA</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>BUY_TIMEOUT/FAILED</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="n">
+        <v>162.3</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-06-04 13:23:32</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>TEST-BUY-a9421dde44d5</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>NIFTY 09 JUN 23350 PUT SEDA</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>BUY_TIMEOUT/FAILED</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" t="n">
+        <v>157.95</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-06-04 13:24:32</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>TEST-BUY-649eabc1b1aa</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>NIFTY 09 JUN 23350 PUT SEDA</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>BUY_TIMEOUT/FAILED</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" t="n">
+        <v>157.95</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-06-04 13:25:33</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>TEST-BUY-6df6e847c129</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>NIFTY 09 JUN 23350 PUT SEDA</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>BUY_TIMEOUT/FAILED</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" t="n">
+        <v>157.95</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-06-04 14:40:46</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>TEST-BUY-02a51acc845a</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>NIFTY 09 JUN 23450 CALL SEDA</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>BUY_TIMEOUT/FAILED</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" t="n">
+        <v>181.25</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-06-04 14:41:46</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>TEST-BUY-106b6f834444</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>NIFTY 09 JUN 23450 CALL SEDA</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>BUY_TIMEOUT/FAILED</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" t="n">
+        <v>181.25</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-06-04 14:42:47</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>TEST-BUY-3c1d17af1af1</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>NIFTY 09 JUN 23450 CALL SEDA</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>BUY_TIMEOUT/FAILED</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" t="n">
+        <v>181.25</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-06-04 14:48:33</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>TEST-BUY-38ecade312a1</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>NIFTY 09 JUN 23450 CALL SEDA</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>BUY_TIMEOUT/FAILED</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" t="n">
+        <v>179.85</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-06-04 14:49:35</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>TEST-BUY-59447f69f2f0</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>NIFTY 09 JUN 23450 CALL SEDA</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>BUY_TIMEOUT/FAILED</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="n">
+        <v>179.85</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-06-04 14:50:36</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>TEST-BUY-aa1735f41422</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>NIFTY 09 JUN 23450 CALL SEDA</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>BUY_TIMEOUT/FAILED</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" t="n">
+        <v>179.85</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
